--- a/templates/reports/약품입고일지.xlsx
+++ b/templates/reports/약품입고일지.xlsx
@@ -1,46 +1,199 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\OneDrive\바탕 화면\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5EE77E2-5B75-4035-8BE5-D117569A09C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="28680" yWindow="-5970" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="템플릿" state="visible" r:id="rId4"/>
+    <sheet name="약품" sheetId="8" r:id="rId1"/>
+    <sheet name="키트" sheetId="9" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">약품!$A$1:$G$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">키트!$A$1:$G$6</definedName>
+    <definedName name="거래사진">약품!$C$8</definedName>
+    <definedName name="날짜">키트!$A$2</definedName>
+    <definedName name="사진1">키트!$C$3</definedName>
+    <definedName name="사진2">키트!$C$5</definedName>
+    <definedName name="알칼리량">키트!$B$6</definedName>
+    <definedName name="암모니아량">키트!$B$3</definedName>
+    <definedName name="약1량">약품!$B$3</definedName>
+    <definedName name="약1명">약품!$A$3</definedName>
+    <definedName name="약1사진">약품!$C$3</definedName>
+    <definedName name="약2량">약품!$B$4</definedName>
+    <definedName name="약2명">약품!$A$4</definedName>
+    <definedName name="약2사진">약품!$C$4</definedName>
+    <definedName name="약3량">약품!$B$5</definedName>
+    <definedName name="약3명">약품!$A$5</definedName>
+    <definedName name="약3사진">약품!$C$5</definedName>
+    <definedName name="약품시트명">약품!$A$1</definedName>
+    <definedName name="인량">키트!$B$5</definedName>
+    <definedName name="질산량">키트!$B$4</definedName>
+    <definedName name="추1량">약품!$B$6</definedName>
+    <definedName name="추1명">약품!$A$6</definedName>
+    <definedName name="추1사진">약품!$C$6</definedName>
+    <definedName name="추2량">약품!$B$7</definedName>
+    <definedName name="추2명">약품!$A$7</definedName>
+    <definedName name="추2사진">약품!$C$7</definedName>
+    <definedName name="키트시트명">키트!$A$1</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
-    <t>약품입고일지 기본 템플릿</t>
+    <t>사진대지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이 파일은 기본 번들 템플릿입니다. 실제 양식은 필요에 따라 교체해주세요.</t>
+    <t>거래명세표</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.02.10.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(   )월 약품입고일지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(   )월 키트입고일지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>암모니아성질소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>질산성질소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인산염인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알칼리도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="바탕체"/>
+      <family val="1"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -48,18 +201,314 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="25">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="쉼표 [0] 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="콤마 [0]_Virus" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="콤마_Virus" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="표준 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="표준 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -72,9 +521,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -112,7 +561,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -184,7 +633,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -216,16 +665,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -347,67 +800,230 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="20.796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="1" customWidth="1"/>
+    <col min="3" max="5" width="10.59765625" style="1"/>
+    <col min="6" max="7" width="10.59765625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.69921875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.59765625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.69921875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="10.59765625" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" ht="55.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+    </row>
+    <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="1:9" ht="107.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="3"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="20"/>
+    </row>
+    <row r="4" spans="1:9" ht="107.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="3"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="20"/>
+    </row>
+    <row r="5" spans="1:9" ht="107.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="3"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="20"/>
+    </row>
+    <row r="6" spans="1:9" ht="107.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="3"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="20"/>
+    </row>
+    <row r="7" spans="1:9" ht="107.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="3"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="20"/>
+    </row>
+    <row r="8" spans="1:9" ht="107.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="23" t="s">
         <v>1</v>
       </c>
-    </row>
+      <c r="B8" s="24"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="22"/>
+    </row>
+    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <mergeCells count="10">
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.44" right="0.25" top="0.97" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C1D44E9-C587-4EC1-B39E-F3731E1916D3}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="20.796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="1" customWidth="1"/>
+    <col min="3" max="5" width="10.59765625" style="1"/>
+    <col min="6" max="7" width="10.59765625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.69921875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.59765625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.69921875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="10.59765625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="55.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+    </row>
+    <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="15"/>
+    </row>
+    <row r="3" spans="1:9" ht="121.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="8"/>
+    </row>
+    <row r="4" spans="1:9" ht="121.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="11"/>
+    </row>
+    <row r="5" spans="1:9" ht="121.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="8"/>
+    </row>
+    <row r="6" spans="1:9" ht="121.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="11"/>
+    </row>
+    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.4"/>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C3:G4"/>
+    <mergeCell ref="C5:G6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:G2"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.46" right="0.25" top="1.53" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>